--- a/templates/flow_answer_template.xlsx
+++ b/templates/flow_answer_template.xlsx
@@ -879,7 +879,7 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Территорию и территориальные ограничения — в поле «Территория страхования»; прочие условия (осмотр, согласование СБ, риски РНПК и т. п.) — в «Примечании».</t>
+          <t>Обязательно укажите территорию и территориальные ограничения в поле «Территория страхования» — без неё ответ не будет принят. Прочие условия (осмотр, согласование СБ, риски РНПК и т. п.) — в «Примечании».</t>
         </is>
       </c>
     </row>
